--- a/outputs/resultats/rbc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/rbc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,6 +532,21 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -573,7 +591,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>La mise à jour des montants titrisés est cruciale pour la conformité réglementaire et l'évaluation des risques financiers.</t>
+          <t>La mise à jour des montants titrisés à 17 milliards de dollars représente un changement significatif dans la divulgation des activités de titrisation, ce qui est crucial pour la conformité réglementaire et l'évaluation des risques.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -582,6 +600,9 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -631,55 +652,89 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:52:01.746040+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Les actifs et passifs interdépendants représentent le passif des titres hypothécaires garantis par la Loi nationale sur l’habitation, y compris les passifs découlant des opérations relatives au programme des obligations hypothécaires du Canada et des prêts hypothécaires grevés correspondants.</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Cette note a été ajoutée pour clarifier la nature des actifs et passifs interdépendants, ce qui est essentiel pour comprendre l'impact des titres hypothécaires garantis par la Loi nationale sur l’habitation sur le bilan.</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Les réserves de fonds propres comprennent la réserve de conservation des fonds propres de 2,5 % et la réserve de fonds propres anticyclique, comme le BSIF le prescrit. La réserve de fonds propres anticyclique, calculée conformément aux lignes directrices sur les normes de fonds propres du BSIF, était de 0,09 % au 31 janvier 2025 (0,08 % au 31 octobre 2024 et 0,06 % au 31 janvier 2024).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Les réserves de fonds propres comprennent la réserve de conservation des fonds propres de 2,5 % et la réserve de fonds propres anticyclique, comme le BSIF le prescrit. La réserve de fonds propres anticyclique, calculée conformément aux lignes directrices sur les normes de fonds propres du BSIF, était de 0,09 % au 30 avril 2025 (0,09 % au 31 janvier 2025 et 0,08 % au 31 octobre 2024).</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>La mise à jour des valeurs de la réserve de fonds propres anticyclique est cruciale pour l'évaluation de la conformité réglementaire et des exigences de capital.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:52:26.015228+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -694,12 +749,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -709,22 +764,18 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>(4) Secteur géographique selon l’emplacement du bien immobilier.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>(4) Les montants sont présentés selon l’emplacement géographique du bien immobilier.</t>
+          <t>Les actifs et passifs interdépendants représentent le passif des titres hypothécaires garantis par la Loi nationale sur l’habitation, y compris les passifs découlant des opérations relatives au programme des obligations hypothécaires du Canada et des prêts hypothécaires grevés correspondants.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>La reformulation précise que les montants sont présentés selon l'emplacement géographique, ce qui peut affecter l'interprétation des données géographiques.</t>
+          <t>Cette note a été ajoutée pour clarifier la nature des actifs et passifs interdépendants, ce qui est essentiel pour comprendre l'impact des titres hypothécaires garantis par la Loi nationale sur l’habitation sur le bilan.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -733,6 +784,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:13.243057+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -767,17 +833,17 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Comprend des marges de crédit sur valeur nette assurées et non assurées totalisant 40 892 millions de dollars et 17 millions, respectivement (40 998 millions et 17 millions, respectivement, au 31 octobre 2024), et sont présentées dans les prêts aux particuliers. Les montants indiqués pour les États-Unis et les autres pays comprennent les prêts à terme garantis par des immeubles résidentiels.</t>
+          <t>(4) Secteur géographique selon l’emplacement du bien immobilier.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Comprend des marges de crédit sur valeur nette assurées et non assurées totalisant 41 470 millions de dollars et 17 millions, respectivement (40 892 millions et 17 millions, respectivement, au 31 janvier 2025), et sont présentées dans les prêts aux particuliers. Les montants indiqués pour les États-Unis et les autres pays comprennent les prêts à terme garantis par des immeubles résidentiels.</t>
+          <t>(4) Les montants sont présentés selon l’emplacement géographique du bien immobilier.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>La modification des montants des marges de crédit sur valeur nette reflète un changement significatif dans l'exposition financière de la banque, nécessitant une attention particulière pour l'analyse des risques.</t>
+          <t>La reformulation précise que les montants sont présentés selon l'emplacement géographique, ce qui peut affecter l'interprétation des données géographiques dans le contexte de la gestion des risques.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -786,6 +852,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:51:15.144829+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -820,17 +901,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Le total consolidé des prêts hypothécaires résidentiels au Canada de 443 milliards de dollars (441 milliards au 31 octobre 2024) comprend des prêts hypothécaires commerciaux de 12 milliards (12 milliards au 31 octobre 2024) dans le secteur Services bancaires aux entreprises, dont une tranche de 9 milliards (9 milliards au 31 octobre 2024) est assurée, et des prêts hypothécaires résidentiels de 18 milliards (18 milliards au 31 octobre 2024) dans le secteur Marchés des Capitaux, dont un montant de 18 milliards (18 milliards au 31 octobre 2024) est détenu à des fins de titrisation. Tous les prêts hypothécaires résidentiels détenus à des fins de titrisation sont assurés (tous assurés au 31 octobre 2024).</t>
+          <t>Comprend des marges de crédit sur valeur nette assurées et non assurées totalisant 40 892 millions de dollars et 17 millions, respectivement (40 998 millions et 17 millions, respectivement, au 31 octobre 2024), et sont présentées dans les prêts aux particuliers. Les montants indiqués pour les États-Unis et les autres pays comprennent les prêts à terme garantis par des immeubles résidentiels.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Le total consolidé des prêts hypothécaires résidentiels au Canada de 445 milliards de dollars (443 milliards au 31 janvier 2025) comprend des prêts hypothécaires commerciaux de 12 milliards (12 milliards au 31 janvier 2025) dans le secteur Services bancaires aux entreprises, dont une tranche de 9 milliards (9 milliards au 31 janvier 2025) est assurée, et des prêts hypothécaires résidentiels de 17 milliards (18 milliards au 31 janvier 2025) dans le secteur Marchés des capitaux, dont un montant de 17 milliards (18 milliards au 31 janvier 2025) est détenu à des fins de titrisation. Tous les prêts hypothécaires résidentiels détenus à des fins de titrisation sont assurés (tous assurés au 31 janvier 2025).</t>
+          <t>Comprend des marges de crédit sur valeur nette assurées et non assurées totalisant 41 470 millions de dollars et 17 millions, respectivement (40 892 millions et 17 millions, respectivement, au 31 janvier 2025), et sont présentées dans les prêts aux particuliers. Les montants indiqués pour les États-Unis et les autres pays comprennent les prêts à terme garantis par des immeubles résidentiels.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Les ajustements des montants totaux des prêts hypothécaires résidentiels indiquent une variation dans le portefeuille de prêts, ce qui est crucial pour l'évaluation de la stratégie de financement et de titrisation de la banque.</t>
+          <t>L'augmentation du montant total des marges de crédit sur valeur nette assurées indique un changement significatif dans l'exposition au risque de crédit, ce qui nécessite une attention particulière pour l'analyse des risques.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -839,6 +920,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:51:19.292490+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -853,12 +949,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -873,17 +969,17 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Selon notre politique, les nouveaux prêts hypothécaires sont accordés avec des périodes d’amortissement de 30 ans ou moins. Les périodes d’amortissement de plus de 30 ans indiquent l’incidence de la hausse des taux d’intérêt sur nos portefeuilles de prêts hypothécaires à taux variables. Pour ces prêts, la période d’amortissement est ramenée au calendrier d’amortissement initial lors du renouvellement. Nous n’offrons pas de produits hypothécaires dont la structure entraînerait un amortissement négatif, car les paiements sur les prêts hypothécaires à taux variables augmentent automatiquement pour assurer la couverture des intérêts courus.</t>
+          <t>Le total consolidé des prêts hypothécaires résidentiels au Canada de 443 milliards de dollars (441 milliards au 31 octobre 2024) comprend des prêts hypothécaires commerciaux de 12 milliards (12 milliards au 31 octobre 2024) dans le secteur Services bancaires aux entreprises, dont une tranche de 9 milliards (9 milliards au 31 octobre 2024) est assurée, et des prêts hypothécaires résidentiels de 18 milliards (18 milliards au 31 octobre 2024) dans le secteur Marchés des Capitaux, dont un montant de 18 milliards (18 milliards au 31 octobre 2024) est détenu à des fins de titrisation. Tous les prêts hypothécaires résidentiels détenus à des fins de titrisation sont assurés (tous assurés au 31 octobre 2024).</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Selon notre politique, les nouveaux prêts hypothécaires sont accordés avec des périodes d’amortissement de 30 ans ou moins. Nous n’offrons pas de produits hypothécaires dont la structure entraînerait un amortissement négatif, car les paiements sur les prêts hypothécaires à taux variables augmentent automatiquement pour assurer la couverture des intérêts courus.</t>
+          <t>Le total consolidé des prêts hypothécaires résidentiels au Canada de 445 milliards de dollars (443 milliards au 31 janvier 2025) comprend des prêts hypothécaires commerciaux de 12 milliards (12 milliards au 31 janvier 2025) dans le secteur Services bancaires aux entreprises, dont une tranche de 9 milliards (9 milliards au 31 janvier 2025) est assurée, et des prêts hypothécaires résidentiels de 17 milliards (18 milliards au 31 janvier 2025) dans le secteur Marchés des capitaux, dont un montant de 17 milliards (18 milliards au 31 janvier 2025) est détenu à des fins de titrisation. Tous les prêts hypothécaires résidentiels détenus à des fins de titrisation sont assurés (tous assurés au 31 janvier 2025).</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>La suppression de la mention concernant les périodes d'amortissement de plus de 30 ans réduit la transparence sur l'impact des taux d'intérêt sur les prêts à taux variables, ce qui peut affecter l'évaluation des risques.</t>
+          <t>La modification des montants consolidés des prêts hypothécaires résidentiels et des prêts à des fins de titrisation reflète un ajustement dans la stratégie de financement et de gestion des risques, nécessitant une réévaluation des impacts sur le bilan.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -892,6 +988,9 @@
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -906,12 +1005,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -926,17 +1025,17 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Avec prise d’effet au premier trimestre de 2025, les titres hypothécaires, les prêts hypothécaires et les autres prêts sont présentés déduction faite de la correction de valeur pour pertes sur prêts. Les montants correspondants ont été révisés par rapport à ceux présentés précédemment afin qu’ils soient conformes à la présentation adoptée pour la période considérée.</t>
+          <t>Selon notre politique, les nouveaux prêts hypothécaires sont accordés avec des périodes d’amortissement de 30 ans ou moins. Les périodes d’amortissement de plus de 30 ans indiquent l’incidence de la hausse des taux d’intérêt sur nos portefeuilles de prêts hypothécaires à taux variables. Pour ces prêts, la période d’amortissement est ramenée au calendrier d’amortissement initial lors du renouvellement. Nous n’offrons pas de produits hypothécaires dont la structure entraînerait un amortissement négatif, car les paiements sur les prêts hypothécaires à taux variables augmentent automatiquement pour assurer la couverture des intérêts courus.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Le montant des actifs donnés en garantie représente les garanties en espèces et les dépôts de garantie obligatoires qui ont été fournis en lien avec des transactions visant des dérivés négociés hors cote et en Bourse.</t>
+          <t>Selon notre politique, les nouveaux prêts hypothécaires sont accordés avec des périodes d’amortissement de 30 ans ou moins. Nous n’offrons pas de produits hypothécaires dont la structure entraînerait un amortissement négatif, car les paiements sur les prêts hypothécaires à taux variables augmentent automatiquement pour assurer la couverture des intérêts courus.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>La reformulation de cette note modifie son contenu de manière significative, passant d'une explication sur la présentation des prêts à une description des garanties, ce qui peut avoir un impact sur l'interprétation des données financières.</t>
+          <t>La suppression de la mention des périodes d'amortissement de plus de 30 ans réduit la transparence sur l'impact des taux d'intérêt sur les prêts à taux variables, ce qui peut affecter l'évaluation des risques.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -945,6 +1044,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:19.642543+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -959,12 +1073,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -979,17 +1093,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Inclut les obligations encaissables par anticipation (garanties) de 4 957 millions de dollars (5 157 millions au 31 octobre 2024), d’autres dépôts structurés à long terme (non garantis) de 23 104 millions (19 777 millions au 31 octobre 2024) et des certificats de placement garanti de gros de 196 millions (192 millions au 31 octobre 2024).</t>
+          <t>Avec prise d’effet au premier trimestre de 2025, les titres hypothécaires, les prêts hypothécaires et les autres prêts sont présentés déduction faite de la correction de valeur pour pertes sur prêts. Les montants correspondants ont été révisés par rapport à ceux présentés précédemment afin qu’ils soient conformes à la présentation adoptée pour la période considérée.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Inclut les obligations encaissables par anticipation (garanties) de 4 715 millions de dollars (4 957 millions au 31 janvier 2025), d’autres dépôts structurés à long terme (non garantis) de 22 718 millions (23 104 millions au 31 janvier 2025), des avances d’une FHLB (garanties) de 2 068 millions (néant au 31 janvier 2025) et des certificats de placement garanti de gros de 202 millions (196 millions au 31 janvier 2025).</t>
+          <t>Le montant des actifs donnés en garantie représente les garanties en espèces et les dépôts de garantie obligatoires qui ont été fournis en lien avec des transactions visant des dérivés négociés hors cote et en Bourse.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>L'ajout des avances d'une FHLB et les modifications des montants financiers indiquent un changement structurel dans la composition des passifs, nécessitant une attention particulière pour l'analyse des risques.</t>
+          <t>La reformulation de cette note modifie l'accent mis sur les actifs donnés en garantie, ce qui peut avoir des implications sur la compréhension des engagements financiers de la banque.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -998,6 +1112,9 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1012,33 +1129,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>De 30 à 35 ans</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>Inclut les obligations encaissables par anticipation (garanties) de 4 957 millions de dollars (5 157 millions au 31 octobre 2024), d’autres dépôts structurés à long terme (non garantis) de 23 104 millions (19 777 millions au 31 octobre 2024) et des certificats de placement garanti de gros de 196 millions (192 millions au 31 octobre 2024).</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Inclut les obligations encaissables par anticipation (garanties) de 4 715 millions de dollars (4 957 millions au 31 janvier 2025), d’autres dépôts structurés à long terme (non garantis) de 22 718 millions (23 104 millions au 31 janvier 2025), des avances d’une FHLB (garanties) de 2 068 millions (néant au 31 janvier 2025) et des certificats de placement garanti de gros de 202 millions (196 millions au 31 janvier 2025).</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>La suppression de cet indicateur modifie la granularité de l'analyse des périodes d'amortissement, ce qui peut affecter l'évaluation des risques associés aux prêts hypothécaires à plus long terme.</t>
+          <t>L'ajout des avances d'une FHLB et les modifications des montants indiquent un changement structurel dans la composition des passifs, nécessitant une attention particulière pour l'analyse des risques.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1047,6 +1168,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:17.668997+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1061,17 +1197,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1081,13 +1217,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Le montant des actifs donnés en garantie représente les garanties en espèces et les dépôts de garantie obligatoires qui ont été fournis en lien avec des transactions visant des dérivés négociés hors cote et en Bourse.</t>
+          <t>De 30 à 35 ans</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>La suppression de cette note pourrait indiquer un changement dans la manière dont les garanties en espèces et les dépôts de garantie sont présentés, ce qui peut affecter la transparence des informations fournies aux investisseurs.</t>
+          <t>La suppression de l'indicateur 'De 30 à 35 ans' modifie la granularité de l'analyse des périodes d'amortissement, ce qui peut affecter l'évaluation des risques associés aux prêts hypothécaires à plus long terme.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1096,11 +1232,26 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:51:23.493267+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1110,33 +1261,33 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Nombre d’actions (en milliers)</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Le montant des actifs donnés en garantie représente les garanties en espèces et les dépôts de garantie obligatoires qui ont été fournis en lien avec des transactions visant des dérivés négociés hors cote et en Bourse.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Cet indicateur a été ajouté pour fournir des informations supplémentaires sur le nombre d'actions en circulation, ce qui est essentiel pour l'analyse des fonds propres.</t>
+          <t>La suppression de cette note pourrait indiquer un changement dans la divulgation des garanties fournies, ce qui peut affecter la transparence des obligations de la banque.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1145,6 +1296,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:51:55.615900+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1185,7 +1351,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Cette note a été ajoutée pour indiquer que certaines données ou résultats ne sont pas significatifs, ce qui est une clarification cosmétique sans impact majeur sur l'analyse des risques.</t>
+          <t>Cette note a été ajoutée pour indiquer que certaines données ne sont pas significatives, ce qui est une clarification mineure sans impact majeur sur l'analyse des risques.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1194,6 +1360,21 @@
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:14.727912+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1243,6 +1424,21 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:50:49.513505+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1292,6 +1488,21 @@
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:50:49.650774+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1341,6 +1552,9 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1353,11 +1567,7 @@
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
           <t>34</t>
@@ -1365,23 +1575,19 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Les revenus tirés des activités de négociation (montant imposable équivalent) dans le graphique ci-dessus excluent l’incidence des engagements de souscription de prêts.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>La suppression d'une ancienne note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1390,11 +1596,26 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:00.956682+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1402,39 +1623,27 @@
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Les réserves de fonds propres comprennent la réserve de conservation des fonds propres de 2,5 % et la réserve de fonds propres anticyclique, comme le BSIF le prescrit. La réserve de fonds propres anticyclique, calculée conformément aux lignes directrices sur les normes de fonds propres du BSIF, était de 0,09 % au 31 janvier 2025 (0,08 % au 31 octobre 2024 et 0,06 % au 31 janvier 2024).</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Les réserves de fonds propres comprennent la réserve de conservation des fonds propres de 2,5 % et la réserve de fonds propres anticyclique, comme le BSIF le prescrit. La réserve de fonds propres anticyclique, calculée conformément aux lignes directrices sur les normes de fonds propres du BSIF, était de 0,09 % au 30 avril 2025 (0,09 % au 31 janvier 2025 et 0,08 % au 31 octobre 2024).</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Les modifications apportées à cette note ne concernent que les mises à jour de dates et de valeurs, ce qui n'affecte pas la compréhension ou l'application des réserves de fonds propres.</t>
+          <t>Nouveau tableau détecté dans le trimestre courant.</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1443,6 +1652,9 @@
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1455,12 +1667,12 @@
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Tableau</t>
@@ -1468,14 +1680,14 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+          <t>Tableau supprimé du trimestre courant.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1484,6 +1696,21 @@
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:52:57.310463+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1493,15 +1720,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>Modèle commun de déclaration du ratio de liquidité à court terme (1)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Tableau</t>
@@ -1509,14 +1736,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Modèle commun de déclaration du ratio de liquidité à court terme (1)</t>
+        </is>
+      </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Nouveau tableau détecté dans le trimestre courant.</t>
+          <t>Tableau supprimé du trimestre courant.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1525,6 +1756,21 @@
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:52:49.152578+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1534,12 +1780,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Programmes par secteur géographique</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -1553,7 +1799,11 @@
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Programmes par secteur géographique</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1566,21 +1816,36 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:05.051743+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Modèle commun de déclaration du ratio de liquidité à court terme (1)</t>
+          <t>Banques d’importance systémique mondiale selon 13 indicateurs d’évaluation (1)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -1596,7 +1861,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Modèle commun de déclaration du ratio de liquidité à court terme (1)</t>
+          <t>Banques d’importance systémique mondiale selon 13 indicateurs d’évaluation (1)</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1611,99 +1876,24 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Programmes par secteur géographique</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Programmes par secteur géographique</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Tableau supprimé du trimestre courant.</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Banques d’importance systémique mondiale selon 13 indicateurs d’évaluation (1)</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Banques d’importance systémique mondiale selon 13 indicateurs d’évaluation (1)</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Tableau supprimé du trimestre courant.</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:53:07.068673+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:N23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/rbc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/rbc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T00:52:01.746040+00:00</t>
+          <t>2026-04-18T23:20:48.438626+00:00</t>
         </is>
       </c>
     </row>
@@ -720,21 +720,9 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:52:26.015228+00:00</t>
-        </is>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -784,21 +772,9 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:53:13.243057+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -864,7 +840,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T00:51:15.144829+00:00</t>
+          <t>2026-04-18T23:20:38.352400+00:00</t>
         </is>
       </c>
     </row>
@@ -920,21 +896,9 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:51:19.292490+00:00</t>
-        </is>
-      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1044,21 +1008,9 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:53:19.642543+00:00</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1168,21 +1120,9 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:53:17.668997+00:00</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1244,7 +1184,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T00:51:23.493267+00:00</t>
+          <t>2026-04-18T23:20:43.462497+00:00</t>
         </is>
       </c>
     </row>
@@ -1296,21 +1236,9 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:51:55.615900+00:00</t>
-        </is>
-      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1360,21 +1288,9 @@
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:53:14.727912+00:00</t>
-        </is>
-      </c>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1436,7 +1352,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:50:49.513505+00:00</t>
+          <t>2026-04-18T23:20:30.924036+00:00</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1416,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:50:49.650774+00:00</t>
+          <t>2026-04-18T23:20:31.085868+00:00</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1524,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:53:00.956682+00:00</t>
+          <t>2026-04-18T23:20:56.657862+00:00</t>
         </is>
       </c>
     </row>
@@ -1652,9 +1568,21 @@
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:21:01.521279+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1708,7 +1636,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:52:57.310463+00:00</t>
+          <t>2026-04-18T23:20:59.604049+00:00</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1696,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:52:49.152578+00:00</t>
+          <t>2026-04-18T23:21:03.752246+00:00</t>
         </is>
       </c>
     </row>
@@ -1816,21 +1744,9 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-10T00:53:05.051743+00:00</t>
-        </is>
-      </c>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1888,7 +1804,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:53:07.068673+00:00</t>
+          <t>2026-04-18T23:20:54.525206+00:00</t>
         </is>
       </c>
     </row>
